--- a/11_Post_Announcement_v2/Project_Southeast_Asia_v2_Valuation.xlsx
+++ b/11_Post_Announcement_v2/Project_Southeast_Asia_v2_Valuation.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="170">
   <si>
     <t xml:space="preserve">Project Southeast Asia - v2 Valuation (post-announcement)</t>
   </si>
@@ -45,7 +45,7 @@
     <t xml:space="preserve">WEIGHTS: fixed on Triangulation before the comparison on Deal_Check, with the logic stated; alternatives are shown for transparency, not selected.</t>
   </si>
   <si>
-    <t xml:space="preserve">LIMITATIONS: FY24/FY25 financials come from media reports (attributed to Nippon Paint), not AkzoNobel's release; the 2026 projection is single-source; country split and country risk premiums are illustrative; comps are dated 2026-09-18; the Information Memorandum and pitch deck valuation slides have NOT been refreshed.</t>
+    <t xml:space="preserve">LIMITATIONS: FY24/FY25 financials come from media reports (reported by several outlets, attributed to Nippon Paint; primary release not read), not in AkzoNobel's release; the 2026 projection is single-source; country split and country risk premiums are illustrative; comps are dated 2026-09-18; the Information Memorandum and pitch deck valuation slides have NOT been refreshed.</t>
   </si>
   <si>
     <t xml:space="preserve">COLOUR CODE: blue = input; black = formula; green = same-workbook link; red = value copied from the model workbook.</t>
@@ -327,13 +327,13 @@
     <t xml:space="preserve">DCF - Buyer case</t>
   </si>
   <si>
-    <t xml:space="preserve">Nippon Paint's 2026 projection (single-source, buyer's view), then a fade. Pasted from model Cases B63 / B61 / B64; Low/High = WACC +/- 0.5pp with g -/+ 0.5pp</t>
+    <t xml:space="preserve">Nippon Paint's 2026 projection (single-source, buyer's view), then a fade. Pasted from model Cases B68 / B66 / B69; Low/High = WACC +/- 0.5pp with g -/+ 0.5pp</t>
   </si>
   <si>
     <t xml:space="preserve">DCF - Downside case</t>
   </si>
   <si>
-    <t xml:space="preserve">3% growth, margin step-down for standalone costs. Pasted from model Cases B89 / B87 / B90; Low/High = WACC +/- 0.5pp with g -/+ 0.5pp</t>
+    <t xml:space="preserve">3% growth, margin step-down for standalone costs. Pasted from model Cases B99 / B97 / B100; Low/High = WACC +/- 0.5pp with g -/+ 0.5pp</t>
   </si>
   <si>
     <t xml:space="preserve">Trading comps - EV/EBITDA (FY25 reported)</t>
@@ -511,9 +511,6 @@
   </si>
   <si>
     <t xml:space="preserve">Terminal growth needed (WACC held)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FY2026E</t>
   </si>
   <si>
     <t xml:space="preserve">Case terminal EBITDA margin (FY2030E)</t>
@@ -3161,11 +3158,11 @@
       <c r="A44" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B44" s="31" t="s">
-        <v>162</v>
-      </c>
-      <c r="C44" s="31" t="s">
-        <v>162</v>
+      <c r="B44" s="31" t="n">
+        <v>0.0571612955661382</v>
+      </c>
+      <c r="C44" s="31" t="n">
+        <v>0.0499498648436709</v>
       </c>
       <c r="D44" s="31" t="n">
         <v>0.0636263740870107</v>
@@ -3173,7 +3170,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B45" s="31" t="n">
         <v>0.223367697594502</v>
@@ -3187,7 +3184,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B46" s="31" t="n">
         <v>0.223367697594502</v>
@@ -3195,7 +3192,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B47" s="32" t="n">
         <v>0.0882196</v>
@@ -3206,7 +3203,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="15" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B49" s="16"/>
       <c r="C49" s="16"/>
@@ -3234,7 +3231,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B52" s="11" t="n">
         <f aca="false">B50-B51</f>
@@ -3243,7 +3240,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B53" s="8" t="n">
         <f aca="false">B52/B50</f>
@@ -3252,7 +3249,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B54" s="11" t="n">
         <f aca="false">B6-1000</f>
@@ -3261,7 +3258,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>
